--- a/JsonConverter/ExcelFiles/Sound.xlsx
+++ b/JsonConverter/ExcelFiles/Sound.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="10260" windowHeight="5856"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -766,7 +766,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -783,9 +783,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1428,7 +1425,7 @@
       <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1471,14 +1468,14 @@
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1492,8 +1489,8 @@
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:8">
@@ -1505,30 +1502,30 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:8">
@@ -1536,8 +1533,8 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1"/>

--- a/JsonConverter/ExcelFiles/Sound.xlsx
+++ b/JsonConverter/ExcelFiles/Sound.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10260" windowHeight="5856"/>
+    <workbookView windowWidth="16524" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>아이디</t>
   </si>
@@ -95,13 +95,52 @@
     <t>BGM_sound_03</t>
   </si>
   <si>
-    <t>GameLobby</t>
+    <t>GamePlay_03</t>
+  </si>
+  <si>
+    <t>Sounds/BGM/GamePlay_03</t>
+  </si>
+  <si>
+    <t>BGM_sound_04</t>
+  </si>
+  <si>
+    <t>Lobby_01</t>
   </si>
   <si>
     <t>Lobby</t>
   </si>
   <si>
-    <t>Sounds/BGM/Lobby</t>
+    <t>Sounds/BGM/Lobby_01</t>
+  </si>
+  <si>
+    <t>BGM_sound_05</t>
+  </si>
+  <si>
+    <t>Lobby_02</t>
+  </si>
+  <si>
+    <t>Sounds/BGM/Lobby_02</t>
+  </si>
+  <si>
+    <t>BGM_sound_06</t>
+  </si>
+  <si>
+    <t>Lobby_03</t>
+  </si>
+  <si>
+    <t>Sounds/BGM/Lobby_03</t>
+  </si>
+  <si>
+    <t>BGM_sound_07</t>
+  </si>
+  <si>
+    <t>MainMenu_01</t>
+  </si>
+  <si>
+    <t>MainMenu</t>
+  </si>
+  <si>
+    <t>Sounds/BGM/MainMenu_01</t>
   </si>
   <si>
     <t>SFX_sound_01</t>
@@ -1319,7 +1358,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
@@ -1433,136 +1472,204 @@
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
-      <c r="B14" s="6"/>
+      <c r="B14" s="1"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Sound.xlsx
+++ b/JsonConverter/ExcelFiles/Sound.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>아이디</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>Sounds/BGM/MainMenu_01</t>
+  </si>
+  <si>
+    <t>BGM_sound_08</t>
+  </si>
+  <si>
+    <t>Intro</t>
+  </si>
+  <si>
+    <t>Sounds/BGM/Intro</t>
   </si>
   <si>
     <t>SFX_sound_01</t>
@@ -1358,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
@@ -1557,61 +1566,69 @@
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:6">
@@ -1626,29 +1643,29 @@
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
+      <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="1"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1"/>
@@ -1671,6 +1688,13 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
